--- a/InputData/fuels/IiFPfOaGL/Increase in Fuel Production from Oil and Gas Leasing.xlsx
+++ b/InputData/fuels/IiFPfOaGL/Increase in Fuel Production from Oil and Gas Leasing.xlsx
@@ -1,28 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ND\fuels\IiFPfOaGL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US States\State Data\ND\fuels\IiFPfOaGL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22C98044-702D-4218-AF73-308ED9B402C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A159DAD-151A-4AEA-A92E-9F461AEA721B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5535" yWindow="3270" windowWidth="21600" windowHeight="12405" activeTab="3" xr2:uid="{F4859696-FEAF-44F6-AC3C-CA46278418D1}"/>
+    <workbookView xWindow="-23910" yWindow="2310" windowWidth="21600" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="4" r:id="rId1"/>
+    <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="natural gas" sheetId="2" r:id="rId2"/>
-    <sheet name="crude oil" sheetId="1" r:id="rId3"/>
-    <sheet name="IiFPfOaGL" sheetId="3" r:id="rId4"/>
+    <sheet name="crude oil" sheetId="3" r:id="rId3"/>
+    <sheet name="IiFPfOaGL" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -40,159 +37,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="128">
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>AK</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>FL</t>
-  </si>
-  <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>HI</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>IN</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>KS</t>
-  </si>
-  <si>
-    <t>KY</t>
-  </si>
-  <si>
-    <t>LA</t>
-  </si>
-  <si>
-    <t>ME</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>NV</t>
-  </si>
-  <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>NJ</t>
-  </si>
-  <si>
-    <t>NM</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>ND</t>
-  </si>
-  <si>
-    <t>OH</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>RI</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>TN</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>UT</t>
-  </si>
-  <si>
-    <t>VT</t>
-  </si>
-  <si>
-    <t>VA</t>
-  </si>
-  <si>
-    <t>WA</t>
-  </si>
-  <si>
-    <t>WV</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>WY</t>
-  </si>
   <si>
     <t>Fuel (BTU)</t>
   </si>
@@ -263,166 +107,319 @@
     <t>IiFPfOaGLS Increase in Fuel Production from Oil and Gas Lease Sales</t>
   </si>
   <si>
-    <t>This file contains increases in natural gas and crude oil production from increased leasing auctions</t>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>AZ</t>
   </si>
   <si>
     <t>State drop-down:</t>
   </si>
   <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
     <t>California</t>
   </si>
   <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
+    <t>CA</t>
   </si>
   <si>
     <t>Colorado</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Connecticut</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>Delaware</t>
   </si>
   <si>
+    <t>DE</t>
+  </si>
+  <si>
     <t>Florida</t>
+  </si>
+  <si>
+    <t>FL</t>
   </si>
   <si>
     <t>Georgia</t>
   </si>
   <si>
+    <t>GA</t>
+  </si>
+  <si>
     <t>Hawaii</t>
+  </si>
+  <si>
+    <t>HI</t>
   </si>
   <si>
     <t>Idaho</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>Illinois</t>
+  </si>
+  <si>
+    <t>IL</t>
   </si>
   <si>
     <t>Indiana</t>
   </si>
   <si>
+    <t>IN</t>
+  </si>
+  <si>
     <t>Iowa</t>
+  </si>
+  <si>
+    <t>IA</t>
   </si>
   <si>
     <t>Kansas</t>
   </si>
   <si>
+    <t>KS</t>
+  </si>
+  <si>
     <t>Kentucky</t>
+  </si>
+  <si>
+    <t>KY</t>
   </si>
   <si>
     <t>Louisiana</t>
   </si>
   <si>
+    <t>LA</t>
+  </si>
+  <si>
     <t>Maine</t>
+  </si>
+  <si>
+    <t>ME</t>
   </si>
   <si>
     <t>Maryland</t>
   </si>
   <si>
+    <t>MD</t>
+  </si>
+  <si>
     <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>MA</t>
   </si>
   <si>
     <t>Michigan</t>
   </si>
   <si>
+    <t>MI</t>
+  </si>
+  <si>
     <t>Minnesota</t>
+  </si>
+  <si>
+    <t>MN</t>
   </si>
   <si>
     <t>Mississippi</t>
   </si>
   <si>
+    <t>MS</t>
+  </si>
+  <si>
     <t>Missouri</t>
+  </si>
+  <si>
+    <t>MO</t>
   </si>
   <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>MT</t>
+  </si>
+  <si>
     <t>Nebraska</t>
+  </si>
+  <si>
+    <t>NE</t>
   </si>
   <si>
     <t>Nevada</t>
   </si>
   <si>
+    <t>NV</t>
+  </si>
+  <si>
     <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>NH</t>
   </si>
   <si>
     <t>New Jersey</t>
   </si>
   <si>
+    <t>NJ</t>
+  </si>
+  <si>
     <t>New Mexico</t>
+  </si>
+  <si>
+    <t>NM</t>
   </si>
   <si>
     <t>New York</t>
   </si>
   <si>
+    <t>NY</t>
+  </si>
+  <si>
     <t>North Carolina</t>
+  </si>
+  <si>
+    <t>NC</t>
   </si>
   <si>
     <t>North Dakota</t>
   </si>
   <si>
+    <t>ND</t>
+  </si>
+  <si>
     <t>Ohio</t>
+  </si>
+  <si>
+    <t>OH</t>
   </si>
   <si>
     <t>Oklahoma</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
     <t>Oregon</t>
+  </si>
+  <si>
+    <t>OR</t>
   </si>
   <si>
     <t>Pennsylvania</t>
   </si>
   <si>
+    <t>PA</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>RI</t>
   </si>
   <si>
     <t>South Carolina</t>
   </si>
   <si>
+    <t>SC</t>
+  </si>
+  <si>
     <t>South Dakota</t>
+  </si>
+  <si>
+    <t>SD</t>
   </si>
   <si>
     <t>Tennessee</t>
   </si>
   <si>
+    <t>TN</t>
+  </si>
+  <si>
     <t>Texas</t>
+  </si>
+  <si>
+    <t>TX</t>
   </si>
   <si>
     <t>Utah</t>
   </si>
   <si>
+    <t>UT</t>
+  </si>
+  <si>
     <t>Vermont</t>
+  </si>
+  <si>
+    <t>VT</t>
   </si>
   <si>
     <t>Virginia</t>
   </si>
   <si>
+    <t>VA</t>
+  </si>
+  <si>
     <t>Washington</t>
+  </si>
+  <si>
+    <t>WA</t>
   </si>
   <si>
     <t>West Virginia</t>
   </si>
   <si>
+    <t>WV</t>
+  </si>
+  <si>
     <t>Wisconsin</t>
   </si>
   <si>
+    <t>WI</t>
+  </si>
+  <si>
     <t>Wyoming</t>
+  </si>
+  <si>
+    <t>WY</t>
   </si>
   <si>
     <t>District</t>
   </si>
   <si>
     <t>DC</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Change in natural gas and crude oil production under the January 2025 Frozen Policies counterfactual, relative to the OBBBA Baseline. Values are NEGATIVE: the frozen-policy world leases less and therefore produces less. Offshore only - onshore leasing is not modelled. Gulf production is allocated to states by BOEM active lease count (TX 427, MS 2, AL 11, LA remainder, of 2206). Includes actual-sale calibration for BBG1, BBG2, BBG3 and BBC1. Built from OilGasLeasing_Calculations_States_406.xlsx; see plan.md and decisions.md in the 'Jan 2025 Frozen Policy Scenario - States' project folder. Revised 2026-08-28: OFFSHORE_POLICY_SCENARIO J38:J64 now apply the BBG1 actual-sale multiplier to future GOA lease sales (2027-2040), reducing the offshore signal to ~55% of the prior values by 2050.</t>
   </si>
 </sst>
 </file>
@@ -808,25 +805,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB036C64-0320-470F-86D8-16CCD5743970}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1">
-        <v>46188</v>
+        <v>46262</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -835,21 +832,21 @@
         <v>ND</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -858,389 +855,389 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G11" s="2" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G12" s="2" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G13" s="2" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G19" s="2" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G21" s="2" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G22" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G25" s="2" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G26" s="2" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G27" s="2" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G28" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G29" s="2" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G30" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G31" s="2" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G32" s="2" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G33" s="2" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G34" s="2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G35" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G36" s="2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G37" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G38" s="2" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G39" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G40" s="2" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G41" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G42" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G43" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G44" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G45" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G46" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G47" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G48" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G49" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G50" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G51" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G52" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1249,13 +1246,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E8A0E54-29F6-4F0E-9451-D99E345114DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AG51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="C1">
         <v>2020</v>
@@ -1353,7 +1350,7 @@
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1380,78 +1377,78 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>25387308667.890816</v>
+        <v>-16069796680.651485</v>
       </c>
       <c r="L2">
-        <v>75062586778.048386</v>
+        <v>-22394377108.570332</v>
       </c>
       <c r="M2">
-        <v>129980541229.67169</v>
+        <v>-58244369634.623055</v>
       </c>
       <c r="N2">
-        <v>202793575142.42477</v>
+        <v>-98058933724.380417</v>
       </c>
       <c r="O2">
-        <v>281116017717.33978</v>
+        <v>-136204868280.36894</v>
       </c>
       <c r="P2">
-        <v>350501295480.75128</v>
+        <v>-186104555889.43283</v>
       </c>
       <c r="Q2">
-        <v>404766480032.61664</v>
+        <v>-216328439448.34616</v>
       </c>
       <c r="R2">
-        <v>490405047068.61804</v>
+        <v>-264097086464.20828</v>
       </c>
       <c r="S2">
-        <v>560953934646.74585</v>
+        <v>-295374750308.79132</v>
       </c>
       <c r="T2">
-        <v>658524116886.09155</v>
+        <v>-349471529167.10565</v>
       </c>
       <c r="U2">
-        <v>751807878552.48083</v>
+        <v>-395287032931.11194</v>
       </c>
       <c r="V2">
-        <v>865464695085.26367</v>
+        <v>-464248463674.89941</v>
       </c>
       <c r="W2">
-        <v>970486682373.40747</v>
+        <v>-515973279212.65558</v>
       </c>
       <c r="X2">
-        <v>1100070973220.3821</v>
+        <v>-590468396319.78003</v>
       </c>
       <c r="Y2">
-        <v>1217615185639.7019</v>
+        <v>-649471794723.7428</v>
       </c>
       <c r="Z2">
-        <v>1330588883464.8838</v>
+        <v>-714318097056.19507</v>
       </c>
       <c r="AA2">
-        <v>1400688375857.6138</v>
+        <v>-743134035358.14355</v>
       </c>
       <c r="AB2">
-        <v>1462606471518.0835</v>
+        <v>-784375194063.34045</v>
       </c>
       <c r="AC2">
-        <v>1484529275400.05</v>
+        <v>-791036930957.99182</v>
       </c>
       <c r="AD2">
-        <v>1508439513676.3721</v>
+        <v>-802011585944.94702</v>
       </c>
       <c r="AE2">
-        <v>1521568851013.4951</v>
+        <v>-796401205337.7533</v>
       </c>
       <c r="AF2">
-        <v>1524047104475.5117</v>
+        <v>-798980652787.7345</v>
       </c>
       <c r="AG2">
-        <v>1503444312292.8774</v>
+        <v>-779372006646.79456</v>
       </c>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1481,75 +1478,75 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>724997724527.34412</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1418601083962.0579</v>
+        <v>-724997724527.34412</v>
       </c>
       <c r="N3">
-        <v>2293316467329.8965</v>
+        <v>-1418601083962.0391</v>
       </c>
       <c r="O3">
-        <v>2772960592345.2432</v>
+        <v>-1568318742802.5271</v>
       </c>
       <c r="P3">
-        <v>3836405204292.501</v>
+        <v>-2804354957437.9048</v>
       </c>
       <c r="Q3">
-        <v>4604712066459.2803</v>
+        <v>-3655293180359.3569</v>
       </c>
       <c r="R3">
-        <v>5418792282782.6055</v>
+        <v>-4274785600284.4028</v>
       </c>
       <c r="S3">
-        <v>6144455926548.7148</v>
+        <v>-4866386160943.3682</v>
       </c>
       <c r="T3">
-        <v>6949695378136.4746</v>
+        <v>-5533483927868.7061</v>
       </c>
       <c r="U3">
-        <v>7474438985913.9902</v>
+        <v>-5880392198370.3574</v>
       </c>
       <c r="V3">
-        <v>7755775639408.4551</v>
+        <v>-6135734053264.1299</v>
       </c>
       <c r="W3">
-        <v>8373220680641.1895</v>
+        <v>-6585583707891.4365</v>
       </c>
       <c r="X3">
-        <v>9153572925217.1172</v>
+        <v>-7245966457265.416</v>
       </c>
       <c r="Y3">
-        <v>10039039480081.078</v>
+        <v>-7983571444118.2412</v>
       </c>
       <c r="Z3">
-        <v>10694359271226.063</v>
+        <v>-8593374327870.2969</v>
       </c>
       <c r="AA3">
-        <v>11404285327839.563</v>
+        <v>-9158178325756.3633</v>
       </c>
       <c r="AB3">
-        <v>11655918180826.803</v>
+        <v>-9662376972284.7949</v>
       </c>
       <c r="AC3">
-        <v>11854908312900.6</v>
+        <v>-9990359687289.5488</v>
       </c>
       <c r="AD3">
-        <v>11672177005076.205</v>
+        <v>-9922149281423.4063</v>
       </c>
       <c r="AE3">
-        <v>11819059096668.504</v>
+        <v>-10017136330665.67</v>
       </c>
       <c r="AF3">
-        <v>11390367505354.012</v>
+        <v>-9892583643636.623</v>
       </c>
       <c r="AG3">
-        <v>10811601491161.482</v>
+        <v>-9403903463956.5176</v>
       </c>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1647,7 +1644,7 @@
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1745,7 +1742,7 @@
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1843,7 +1840,7 @@
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1941,7 +1938,7 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2039,7 +2036,7 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2137,7 +2134,7 @@
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2235,7 +2232,7 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2333,7 +2330,7 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2431,7 +2428,7 @@
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2529,7 +2526,7 @@
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2627,7 +2624,7 @@
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2725,7 +2722,7 @@
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2823,7 +2820,7 @@
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2921,7 +2918,7 @@
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3019,7 +3016,7 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3046,78 +3043,78 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>4075817009769.3452</v>
+        <v>-2579932812548.582</v>
       </c>
       <c r="L19">
-        <v>12050957113635.385</v>
+        <v>-3595315452157.3721</v>
       </c>
       <c r="M19">
-        <v>20867785073780.902</v>
+        <v>-9350868797703.9004</v>
       </c>
       <c r="N19">
-        <v>32557586700136.316</v>
+        <v>-15742916087023.07</v>
       </c>
       <c r="O19">
-        <v>45131898844434.586</v>
+        <v>-21867072489375.602</v>
       </c>
       <c r="P19">
-        <v>56271389801725.633</v>
+        <v>-29878240518249.219</v>
       </c>
       <c r="Q19">
-        <v>64983418521597.266</v>
+        <v>-34730547642343.328</v>
       </c>
       <c r="R19">
-        <v>78732301193032.109</v>
+        <v>-42399586790525.625</v>
       </c>
       <c r="S19">
-        <v>90058604416936.984</v>
+        <v>-47421073549574.289</v>
       </c>
       <c r="T19">
-        <v>105723053674634.92</v>
+        <v>-56106065500828.156</v>
       </c>
       <c r="U19">
-        <v>120699337593074.3</v>
+        <v>-63461536377849.617</v>
       </c>
       <c r="V19">
-        <v>138946422865520.88</v>
+        <v>-74532980622715.125</v>
       </c>
       <c r="W19">
-        <v>155807225551961.91</v>
+        <v>-82837164644504.609</v>
       </c>
       <c r="X19">
-        <v>176611394427942.88</v>
+        <v>-94797017081884.875</v>
       </c>
       <c r="Y19">
-        <v>195482583439989.16</v>
+        <v>-104269744498375.34</v>
       </c>
       <c r="Z19">
-        <v>213619997109014.06</v>
+        <v>-114680523581930.98</v>
       </c>
       <c r="AA19">
-        <v>224874151978607.59</v>
+        <v>-119306791494771.84</v>
       </c>
       <c r="AB19">
-        <v>234814820791002.16</v>
+        <v>-125927872065078.48</v>
       </c>
       <c r="AC19">
-        <v>238334427305133.31</v>
+        <v>-126997383642892.27</v>
       </c>
       <c r="AD19">
-        <v>242173107377497.22</v>
+        <v>-128759314616252.09</v>
       </c>
       <c r="AE19">
-        <v>244280962808162.06</v>
+        <v>-127858593511498.22</v>
       </c>
       <c r="AF19">
-        <v>244678835136705</v>
+        <v>-128272712074831.36</v>
       </c>
       <c r="AG19">
-        <v>241371150500834.22</v>
+        <v>-125124633067112.84</v>
       </c>
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3215,7 +3212,7 @@
     </row>
     <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3313,7 +3310,7 @@
     </row>
     <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3411,7 +3408,7 @@
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3509,7 +3506,7 @@
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3607,7 +3604,7 @@
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3634,78 +3631,78 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>4615874303.2806253</v>
+        <v>-2921781214.6691093</v>
       </c>
       <c r="L25">
-        <v>13647743050.554251</v>
+        <v>-4071704928.8315473</v>
       </c>
       <c r="M25">
-        <v>23632825678.149876</v>
+        <v>-10589885388.113281</v>
       </c>
       <c r="N25">
-        <v>36871559116.829941</v>
+        <v>-17828897040.800488</v>
       </c>
       <c r="O25">
-        <v>51112003221.380753</v>
+        <v>-24764521505.517578</v>
       </c>
       <c r="P25">
-        <v>63727508269.273758</v>
+        <v>-33837191979.897457</v>
       </c>
       <c r="Q25">
-        <v>73593905460.533569</v>
+        <v>-39332443536.062363</v>
       </c>
       <c r="R25">
-        <v>89164554012.478317</v>
+        <v>-48017652084.399773</v>
       </c>
       <c r="S25">
-        <v>101991624481.20801</v>
+        <v>-53704500056.142723</v>
       </c>
       <c r="T25">
-        <v>119731657615.62294</v>
+        <v>-63540278030.381111</v>
       </c>
       <c r="U25">
-        <v>136692341554.95258</v>
+        <v>-71870369623.835068</v>
       </c>
       <c r="V25">
-        <v>157357217288.15344</v>
+        <v>-84408811577.253281</v>
       </c>
       <c r="W25">
-        <v>176452124067.82059</v>
+        <v>-93813323493.206635</v>
       </c>
       <c r="X25">
-        <v>200012904221.81134</v>
+        <v>-107357890239.96233</v>
       </c>
       <c r="Y25">
-        <v>221384579207.15607</v>
+        <v>-118085780858.86348</v>
       </c>
       <c r="Z25">
-        <v>241925251538.97034</v>
+        <v>-129876017646.58092</v>
       </c>
       <c r="AA25">
-        <v>254670613792.19626</v>
+        <v>-135115279156.02957</v>
       </c>
       <c r="AB25">
-        <v>265928449366.8179</v>
+        <v>-142613671647.88065</v>
       </c>
       <c r="AC25">
-        <v>269914413709.12082</v>
+        <v>-143824896537.81323</v>
       </c>
       <c r="AD25">
-        <v>274261729759.36353</v>
+        <v>-145820288353.62845</v>
       </c>
       <c r="AE25">
-        <v>276648882002.44904</v>
+        <v>-144800219152.31589</v>
       </c>
       <c r="AF25">
-        <v>277099473541.04608</v>
+        <v>-145269209597.76587</v>
       </c>
       <c r="AG25">
-        <v>273353511325.98233</v>
+        <v>-141704001208.50464</v>
       </c>
     </row>
     <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3803,7 +3800,7 @@
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3901,7 +3898,7 @@
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3999,7 +3996,7 @@
     </row>
     <row r="29" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -4097,7 +4094,7 @@
     </row>
     <row r="30" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -4195,7 +4192,7 @@
     </row>
     <row r="31" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4293,7 +4290,7 @@
     </row>
     <row r="32" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -4391,7 +4388,7 @@
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -4489,7 +4486,7 @@
     </row>
     <row r="34" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4587,7 +4584,7 @@
     </row>
     <row r="35" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4685,7 +4682,7 @@
     </row>
     <row r="36" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4783,7 +4780,7 @@
     </row>
     <row r="37" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4881,7 +4878,7 @@
     </row>
     <row r="38" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -4979,7 +4976,7 @@
     </row>
     <row r="39" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -5077,7 +5074,7 @@
     </row>
     <row r="40" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -5175,7 +5172,7 @@
     </row>
     <row r="41" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -5273,7 +5270,7 @@
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -5371,7 +5368,7 @@
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -5469,7 +5466,7 @@
     </row>
     <row r="44" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -5496,78 +5493,78 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>985489163743.77429</v>
+        <v>-623800289330.82788</v>
       </c>
       <c r="L44">
-        <v>2913793141292.3657</v>
+        <v>-869309002305.32227</v>
       </c>
       <c r="M44">
-        <v>5045608282278.8682</v>
+        <v>-2260940530362.1538</v>
       </c>
       <c r="N44">
-        <v>7872077871437.2529</v>
+        <v>-3806469518209.9912</v>
       </c>
       <c r="O44">
-        <v>10912412687754.006</v>
+        <v>-5287225341428.8779</v>
       </c>
       <c r="P44">
-        <v>13605823015479.518</v>
+        <v>-7224240487708.0527</v>
       </c>
       <c r="Q44">
-        <v>15712298815810.803</v>
+        <v>-8397476694949.3682</v>
       </c>
       <c r="R44">
-        <v>19036632281667.363</v>
+        <v>-10251768720019.5</v>
       </c>
       <c r="S44">
-        <v>21775211826745.16</v>
+        <v>-11465910761986.529</v>
       </c>
       <c r="T44">
-        <v>25562708900945.051</v>
+        <v>-13565849359486.766</v>
       </c>
       <c r="U44">
-        <v>29183814921994.699</v>
+        <v>-15344323914689.576</v>
       </c>
       <c r="V44">
-        <v>33595765891040.359</v>
+        <v>-18021281271743.699</v>
       </c>
       <c r="W44">
-        <v>37672528488498.07</v>
+        <v>-20029144565800.379</v>
       </c>
       <c r="X44">
-        <v>42702755051376.828</v>
+        <v>-22920909566231.535</v>
       </c>
       <c r="Y44">
-        <v>47265607660744.727</v>
+        <v>-25211314213367.09</v>
       </c>
       <c r="Z44">
-        <v>51651041203594.977</v>
+        <v>-27728529767545.02</v>
       </c>
       <c r="AA44">
-        <v>54372176044657.531</v>
+        <v>-28847112099811.703</v>
       </c>
       <c r="AB44">
-        <v>56775723939840.117</v>
+        <v>-30448018896822.465</v>
       </c>
       <c r="AC44">
-        <v>57626727326892.227</v>
+        <v>-30706615410823.832</v>
       </c>
       <c r="AD44">
-        <v>58554879303618.945</v>
+        <v>-31132631563499.203</v>
       </c>
       <c r="AE44">
-        <v>59064536307522.633</v>
+        <v>-30914846789020.219</v>
       </c>
       <c r="AF44">
-        <v>59160737601003.891</v>
+        <v>-31014976249124.008</v>
       </c>
       <c r="AG44">
-        <v>58360974668095.203</v>
+        <v>-30253804258016.504</v>
       </c>
     </row>
     <row r="45" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5665,7 +5662,7 @@
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -5763,7 +5760,7 @@
     </row>
     <row r="47" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -5861,7 +5858,7 @@
     </row>
     <row r="48" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -5959,7 +5956,7 @@
     </row>
     <row r="49" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -6057,7 +6054,7 @@
     </row>
     <row r="50" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -6155,7 +6152,7 @@
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -6257,13 +6254,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D423897-148A-4C4A-B58E-29BFA201124C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:AG51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="C1">
         <v>2020</v>
@@ -6361,7 +6358,7 @@
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -6388,78 +6385,78 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>107634684581.35045</v>
+        <v>-68131187895.377068</v>
       </c>
       <c r="L2">
-        <v>318243180378.44891</v>
+        <v>-94945539442.987411</v>
       </c>
       <c r="M2">
-        <v>551079074194.03162</v>
+        <v>-246938910944.75479</v>
       </c>
       <c r="N2">
-        <v>859784815363.3634</v>
+        <v>-415740893998.92865</v>
       </c>
       <c r="O2">
-        <v>1191848820748.0491</v>
+        <v>-577468381055.91626</v>
       </c>
       <c r="P2">
-        <v>1486021889046.0186</v>
+        <v>-789028306795.78271</v>
       </c>
       <c r="Q2">
-        <v>1716090231437.1531</v>
+        <v>-917168639284.19177</v>
       </c>
       <c r="R2">
-        <v>2079172441982.6321</v>
+        <v>-1119693582817.762</v>
       </c>
       <c r="S2">
-        <v>2378278871946.5684</v>
+        <v>-1252301632233.1733</v>
       </c>
       <c r="T2">
-        <v>2791947604117.7769</v>
+        <v>-1481655984262.282</v>
       </c>
       <c r="U2">
-        <v>3187443180071.8462</v>
+        <v>-1675900177732.6792</v>
       </c>
       <c r="V2">
-        <v>3669314486639.6689</v>
+        <v>-1968276259951.2629</v>
       </c>
       <c r="W2">
-        <v>4114576669557.4946</v>
+        <v>-2187574188623.8364</v>
       </c>
       <c r="X2">
-        <v>4663975759255.6377</v>
+        <v>-2503411465334.623</v>
       </c>
       <c r="Y2">
-        <v>5162328475316.7998</v>
+        <v>-2753568433901.9731</v>
       </c>
       <c r="Z2">
-        <v>5641303560485.6699</v>
+        <v>-3028497588036.9233</v>
       </c>
       <c r="AA2">
-        <v>5938504687698.9287</v>
+        <v>-3150668648806.814</v>
       </c>
       <c r="AB2">
-        <v>6201019111085.749</v>
+        <v>-3325518971346.9448</v>
       </c>
       <c r="AC2">
-        <v>6293965319438.7705</v>
+        <v>-3353762766654.2856</v>
       </c>
       <c r="AD2">
-        <v>6395337662163.5234</v>
+        <v>-3400292059828.4302</v>
       </c>
       <c r="AE2">
-        <v>6451002171605.1602</v>
+        <v>-3376505704412.1807</v>
       </c>
       <c r="AF2">
-        <v>6461509233743.5645</v>
+        <v>-3387441799147.7466</v>
       </c>
       <c r="AG2">
-        <v>6374159484816.3604</v>
+        <v>-3304306935580.312</v>
       </c>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6489,75 +6486,75 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>10830244247839.193</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>21191509586563.902</v>
+        <v>-10830244247839.18</v>
       </c>
       <c r="N3">
-        <v>34258283355256.77</v>
+        <v>-21191509586563.898</v>
       </c>
       <c r="O3">
-        <v>41423358293035.602</v>
+        <v>-23428039107417.559</v>
       </c>
       <c r="P3">
-        <v>57309428692699.234</v>
+        <v>-41892337202150.063</v>
       </c>
       <c r="Q3">
-        <v>68786638472884.219</v>
+        <v>-54603920262731.07</v>
       </c>
       <c r="R3">
-        <v>80947625027515.484</v>
+        <v>-63858093055959.094</v>
       </c>
       <c r="S3">
-        <v>91787816986583.5</v>
+        <v>-72695608474745.094</v>
       </c>
       <c r="T3">
-        <v>103816737414405.42</v>
+        <v>-82660924928254.734</v>
       </c>
       <c r="U3">
-        <v>111655522623597.56</v>
+        <v>-87843149884309.328</v>
       </c>
       <c r="V3">
-        <v>115858218121988.47</v>
+        <v>-91657526897697.516</v>
       </c>
       <c r="W3">
-        <v>125081806527769.16</v>
+        <v>-98377522657126.984</v>
       </c>
       <c r="X3">
-        <v>136738954022427.2</v>
+        <v>-108242528064478.41</v>
       </c>
       <c r="Y3">
-        <v>149966332175539.78</v>
+        <v>-119261103565868.09</v>
       </c>
       <c r="Z3">
-        <v>159755705518980.44</v>
+        <v>-128370531017350.2</v>
       </c>
       <c r="AA3">
-        <v>170360804446762.53</v>
+        <v>-136807750945523.09</v>
       </c>
       <c r="AB3">
-        <v>174119775222028.13</v>
+        <v>-144339629055751.41</v>
       </c>
       <c r="AC3">
-        <v>177092352459665.78</v>
+        <v>-149239138105778.81</v>
       </c>
       <c r="AD3">
-        <v>174362654657157.91</v>
+        <v>-148220189589414.41</v>
       </c>
       <c r="AE3">
-        <v>176556825581784.66</v>
+        <v>-149639136034171.81</v>
       </c>
       <c r="AF3">
-        <v>170152895632959.34</v>
+        <v>-147778528784502.5</v>
       </c>
       <c r="AG3">
-        <v>161507106709773.88</v>
+        <v>-140478470417472.8</v>
       </c>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6655,7 +6652,7 @@
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -6753,7 +6750,7 @@
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6851,7 +6848,7 @@
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -6949,7 +6946,7 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7047,7 +7044,7 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7145,7 +7142,7 @@
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -7243,7 +7240,7 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -7341,7 +7338,7 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -7439,7 +7436,7 @@
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -7537,7 +7534,7 @@
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -7635,7 +7632,7 @@
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -7733,7 +7730,7 @@
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -7831,7 +7828,7 @@
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -7929,7 +7926,7 @@
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -8027,7 +8024,7 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -8054,78 +8051,78 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>17280259360970.994</v>
+        <v>-10938152529384.967</v>
       </c>
       <c r="L19">
-        <v>51092496049851.719</v>
+        <v>-15243074786937.469</v>
       </c>
       <c r="M19">
-        <v>88473240456970.609</v>
+        <v>-39644919702584.844</v>
       </c>
       <c r="N19">
-        <v>138034543993792.84</v>
+        <v>-66745310800191.422</v>
       </c>
       <c r="O19">
-        <v>191345910676463.94</v>
+        <v>-92709923722250.031</v>
       </c>
       <c r="P19">
-        <v>238574059641393.69</v>
+        <v>-126674908163759.28</v>
       </c>
       <c r="Q19">
-        <v>275510486247093.81</v>
+        <v>-147247256088716.47</v>
       </c>
       <c r="R19">
-        <v>333801684776490.19</v>
+        <v>-179761715205106.06</v>
       </c>
       <c r="S19">
-        <v>381821862532496.63</v>
+        <v>-201051334774889.84</v>
       </c>
       <c r="T19">
-        <v>448234497170161.44</v>
+        <v>-237873133473380.97</v>
       </c>
       <c r="U19">
-        <v>511729514182423.63</v>
+        <v>-269058155806901.41</v>
       </c>
       <c r="V19">
-        <v>589091762127768.88</v>
+        <v>-315997806824902.81</v>
       </c>
       <c r="W19">
-        <v>660576581676217.38</v>
+        <v>-351205092464518.25</v>
       </c>
       <c r="X19">
-        <v>748780108258668</v>
+        <v>-401911331616449.63</v>
       </c>
       <c r="Y19">
-        <v>828788371582668.38</v>
+        <v>-442072895842807.75</v>
       </c>
       <c r="Z19">
-        <v>905685644347057.75</v>
+        <v>-486211521861200.63</v>
       </c>
       <c r="AA19">
-        <v>953399934406934</v>
+        <v>-505825530344802.88</v>
       </c>
       <c r="AB19">
-        <v>995545431834311</v>
+        <v>-533896954854428.06</v>
       </c>
       <c r="AC19">
-        <v>1010467523102630.5</v>
+        <v>-538431367810133.5</v>
       </c>
       <c r="AD19">
-        <v>1026742391943710.8</v>
+        <v>-545901434332454.88</v>
       </c>
       <c r="AE19">
-        <v>1035679075914069.1</v>
+        <v>-542082643090174.06</v>
       </c>
       <c r="AF19">
-        <v>1037365936981015.5</v>
+        <v>-543838383390447.06</v>
       </c>
       <c r="AG19">
-        <v>1023342331835066.5</v>
+        <v>-530491458930439.38</v>
       </c>
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -8223,7 +8220,7 @@
     </row>
     <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -8321,7 +8318,7 @@
     </row>
     <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -8419,7 +8416,7 @@
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -8517,7 +8514,7 @@
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -8615,7 +8612,7 @@
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -8642,78 +8639,78 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>19569942651.166187</v>
+        <v>-12387488708.25211</v>
       </c>
       <c r="L25">
-        <v>57862396432.468376</v>
+        <v>-17262825353.270149</v>
       </c>
       <c r="M25">
-        <v>100196195308.02888</v>
+        <v>-44897983808.136078</v>
       </c>
       <c r="N25">
-        <v>156324511884.27563</v>
+        <v>-75589253454.350372</v>
       </c>
       <c r="O25">
-        <v>216699785590.59601</v>
+        <v>-104994251101.07597</v>
       </c>
       <c r="P25">
-        <v>270185798008.42715</v>
+        <v>-143459692144.69037</v>
       </c>
       <c r="Q25">
-        <v>312016405715.9339</v>
+        <v>-166757934415.30646</v>
       </c>
       <c r="R25">
-        <v>378031353087.87616</v>
+        <v>-203580651421.41214</v>
       </c>
       <c r="S25">
-        <v>432414340353.84753</v>
+        <v>-227691205860.57666</v>
       </c>
       <c r="T25">
-        <v>507626837112.27679</v>
+        <v>-269391997138.59555</v>
       </c>
       <c r="U25">
-        <v>579535123649.32947</v>
+        <v>-304709123224.12292</v>
       </c>
       <c r="V25">
-        <v>667148088479.85657</v>
+        <v>-357868410900.22992</v>
       </c>
       <c r="W25">
-        <v>748104849010.34717</v>
+        <v>-397740761567.97028</v>
       </c>
       <c r="X25">
-        <v>847995592591.87854</v>
+        <v>-455165720969.93054</v>
       </c>
       <c r="Y25">
-        <v>938605177330.23938</v>
+        <v>-500648806163.99451</v>
       </c>
       <c r="Z25">
-        <v>1025691556451.954</v>
+        <v>-550635925097.61951</v>
       </c>
       <c r="AA25">
-        <v>1079728125036.1595</v>
+        <v>-572848845237.60376</v>
       </c>
       <c r="AB25">
-        <v>1127458020197.4458</v>
+        <v>-604639812972.17212</v>
       </c>
       <c r="AC25">
-        <v>1144357330807.1487</v>
+        <v>-609775048482.59631</v>
       </c>
       <c r="AD25">
-        <v>1162788665847.9919</v>
+        <v>-618234919968.80786</v>
       </c>
       <c r="AE25">
-        <v>1172909485746.469</v>
+        <v>-613910128074.94312</v>
       </c>
       <c r="AF25">
-        <v>1174819860680.6689</v>
+        <v>-615898508935.95422</v>
       </c>
       <c r="AG25">
-        <v>1158938088148.4617</v>
+        <v>-600783079196.42151</v>
       </c>
     </row>
     <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -8811,7 +8808,7 @@
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -8909,7 +8906,7 @@
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -9007,7 +9004,7 @@
     </row>
     <row r="29" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -9105,7 +9102,7 @@
     </row>
     <row r="30" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -9203,7 +9200,7 @@
     </row>
     <row r="31" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -9301,7 +9298,7 @@
     </row>
     <row r="32" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -9399,7 +9396,7 @@
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -9497,7 +9494,7 @@
     </row>
     <row r="34" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -9595,7 +9592,7 @@
     </row>
     <row r="35" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -9693,7 +9690,7 @@
     </row>
     <row r="36" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -9791,7 +9788,7 @@
     </row>
     <row r="37" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -9889,7 +9886,7 @@
     </row>
     <row r="38" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -9987,7 +9984,7 @@
     </row>
     <row r="39" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -10085,7 +10082,7 @@
     </row>
     <row r="40" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -10183,7 +10180,7 @@
     </row>
     <row r="41" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -10281,7 +10278,7 @@
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -10379,7 +10376,7 @@
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -10477,7 +10474,7 @@
     </row>
     <row r="44" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -10504,78 +10501,78 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>4178182756021.8574</v>
+        <v>-2644728839211.4219</v>
       </c>
       <c r="L44">
-        <v>12353621638327.648</v>
+        <v>-3685613212923.166</v>
       </c>
       <c r="M44">
-        <v>21391887698259.563</v>
+        <v>-9585719543037.2148</v>
       </c>
       <c r="N44">
-        <v>33375283287287.355</v>
+        <v>-16138305612503.824</v>
       </c>
       <c r="O44">
-        <v>46265404223584.414</v>
+        <v>-22416272610079.695</v>
       </c>
       <c r="P44">
-        <v>57684667874787.672</v>
+        <v>-30628644272890.832</v>
       </c>
       <c r="Q44">
-        <v>66615502620333.547</v>
+        <v>-35602818997668.133</v>
       </c>
       <c r="R44">
-        <v>80709693884236.25</v>
+        <v>-43464469078471.266</v>
       </c>
       <c r="S44">
-        <v>92320461665558.359</v>
+        <v>-48612072451233.25</v>
       </c>
       <c r="T44">
-        <v>108378329723476.13</v>
+        <v>-57515191389090.383</v>
       </c>
       <c r="U44">
-        <v>123730748899147.78</v>
+        <v>-65055397808350.43</v>
       </c>
       <c r="V44">
-        <v>142436116890462.84</v>
+        <v>-76404905727199</v>
       </c>
       <c r="W44">
-        <v>159720385263728.75</v>
+        <v>-84917652594761.703</v>
       </c>
       <c r="X44">
-        <v>181047059018375.34</v>
+        <v>-97177881427080.297</v>
       </c>
       <c r="Y44">
-        <v>200392205360022.16</v>
+        <v>-106888520116012.89</v>
       </c>
       <c r="Z44">
-        <v>218985147302487.78</v>
+        <v>-117560770008342.34</v>
       </c>
       <c r="AA44">
-        <v>230521954695221.41</v>
+        <v>-122303228458228.05</v>
       </c>
       <c r="AB44">
-        <v>240712287312146.5</v>
+        <v>-129090600069558.7</v>
       </c>
       <c r="AC44">
-        <v>244320290127306.53</v>
+        <v>-130186972851034.45</v>
       </c>
       <c r="AD44">
-        <v>248255380158530.34</v>
+        <v>-131993155413339.89</v>
       </c>
       <c r="AE44">
-        <v>250416175206855.94</v>
+        <v>-131069812344000.13</v>
       </c>
       <c r="AF44">
-        <v>250824040255319.09</v>
+        <v>-131494331657826.11</v>
       </c>
       <c r="AG44">
-        <v>247433281819690.44</v>
+        <v>-128267187408435.83</v>
       </c>
     </row>
     <row r="45" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -10673,7 +10670,7 @@
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -10771,7 +10768,7 @@
     </row>
     <row r="47" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -10869,7 +10866,7 @@
     </row>
     <row r="48" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -10967,7 +10964,7 @@
     </row>
     <row r="49" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -11065,7 +11062,7 @@
     </row>
     <row r="50" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -11163,7 +11160,7 @@
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -11265,7 +11262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E50148E-64F2-4F1B-94D1-CDE727BFDAA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -11277,7 +11274,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -11372,7 +11369,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -11467,7 +11464,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -11562,7 +11559,7 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <f>SUMIFS('natural gas'!D:D,'natural gas'!$B:$B,About!$B$2)</f>
@@ -11687,7 +11684,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -11782,7 +11779,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -11877,7 +11874,7 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -11972,7 +11969,7 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -12067,7 +12064,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -12162,7 +12159,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -12257,7 +12254,7 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -12352,7 +12349,7 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -12447,7 +12444,7 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -12542,7 +12539,7 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -12637,7 +12634,7 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -12732,7 +12729,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -12827,7 +12824,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -12922,7 +12919,7 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
         <f>SUMIFS('crude oil'!D:D,'crude oil'!$B:$B,About!$B$2)</f>
@@ -13047,7 +13044,7 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -13142,7 +13139,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -13237,7 +13234,7 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -13332,7 +13329,7 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -13428,10 +13425,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" enabled="0" method="" siteId="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" removed="1"/>
-</clbl:labelList>
 </file>